--- a/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_5602_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_5602_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB3"/>
+  <dimension ref="A1:BB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,181 +867,1483 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5602-04-04-04-FG</t>
+          <t>5602-02-02-02-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="C3" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="D3" t="n">
-        <v>0.26092</v>
+        <v>0.19657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4018</v>
+        <v>0.2639</v>
       </c>
       <c r="F3" t="n">
         <v>1.7899</v>
       </c>
       <c r="G3" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.19463</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.19463</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>5602-02-02-02-FG</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Male Run Pipe Tee, 1/8-27 NPTF x 1/8-27 NPTF (female) x 1/8-27 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>1/8-27 NPTF</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1/8-27 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1/8-27 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-02-02-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-02-02-02 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-02-02-02-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>5602-02-02-02-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5602-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.1582</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>0.88</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>0.375</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>0.88</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>0.375</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>0.28</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" t="n">
         <v>1.09</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N4" t="n">
         <v>0.43</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O4" t="n">
         <v>0.67</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P4" t="n">
         <v>0.28</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q4" t="n">
         <v>0.88</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>0.43</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>0.67</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>0.28</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>0.88</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V4" t="n">
         <v>0.52183</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W4" t="n">
         <v>0.4018</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X4" t="n">
         <v>0.05556</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y4" t="n">
         <v>0.26092</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z4" t="n">
         <v>0.21647</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AB4" t="n">
         <v>0.43</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AC4" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD4" t="n">
         <v>0.05556</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE4" t="n">
         <v>0.215</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AF4" t="n">
         <v>0.25944</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG4" t="n">
         <v>0.88</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH4" t="n">
         <v>0.43</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI4" t="n">
         <v>0.67</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AJ4" t="n">
         <v>0.05556</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK4" t="n">
         <v>0.215</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL4" t="n">
         <v>0.25944</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AM4" t="n">
         <v>0.88</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN4" t="n">
         <v>0.75</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AO4" t="n">
         <v>0.53</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AP4" t="n">
         <v>0.62</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ4" t="n">
         <v>0.75</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR4" t="n">
         <v>0.62</v>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>5602-04-04-04-FG</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>Male Run Pipe Tee, 1/4-18 NPTF x 1/4-18 NPTF (female) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>5602</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>1/4-18 NPTF</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>Air-Way s189 only (double-pass 14 rows; 8-8-8 and 20-20-20 print out of size order on page) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>5602-04-04-04-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5602-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>5602-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>Male Run Pipe Tee, 3/8-18 NPTF x 3/8-18 NPTF (female) x 3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-06-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-06-06-06 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-06-06-06-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -06 0.57 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>5602-06-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5602-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>5602-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Male Run Pipe Tee, 3/4-14 NPTF x 3/4-14 NPTF (female) x 3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-12-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-12-12-12 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-12-12-12-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>5602-12-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5602-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.2832</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.57203</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.63957</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.63957</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>5602-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>Male Run Pipe Tee, 1-11 1/2 NPTF x 1-11 1/2 NPTF (female) x 1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-16-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-16-16-16 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-16-16-16-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>5602-16-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5602-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.80957</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.80957</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>5602-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>Male Run Pipe Tee, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPTF (female) x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-20-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-20-20-20 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-20-20-20-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>5602-20-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5602-24-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.92957</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.92957</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>5602-24-24-24-FG</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>Male Run Pipe Tee, 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPTF (female) x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-24-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-24-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-24-24-24-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>5602-24-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5602-32-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.16957</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.16957</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>5602-32-32-32-FG</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>Male Run Pipe Tee, 2-11 1/2 NPTF x 2-11 1/2 NPTF (female) x 2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-32-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: Air-Way tap drill to MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)), tapered helix over P1; connecting drill to the axis crossing = the part's own D column (ASSUMPTION); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-32-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-32-32-32-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>5602-32-32-32-FG</t>
         </is>
       </c>
     </row>
